--- a/olympic_simulator/media/simulacion_Copa Libertadores_1880.xlsx
+++ b/olympic_simulator/media/simulacion_Copa Libertadores_1880.xlsx
@@ -489,29 +489,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -551,29 +551,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -598,10 +598,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
         <v>-8</v>
@@ -639,16 +639,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -657,12 +657,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -675,34 +675,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -711,145 +711,145 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -926,29 +926,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -957,29 +957,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -988,29 +988,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1035,13 +1035,13 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1112,29 +1112,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
         <v>14</v>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1159,13 +1159,13 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -1205,26 +1205,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1236,29 +1236,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1298,29 +1298,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
         <v>12</v>
       </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10</v>
-      </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1407,13 +1407,13 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
         <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1422,29 +1422,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1453,29 +1453,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1484,29 +1484,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1515,26 +1515,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8</v>
       </c>
       <c r="I22" t="n">
         <v>-1</v>
@@ -1546,29 +1546,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1577,29 +1577,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -1608,29 +1608,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="26">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBC Melgar</t>
+          <t>Club Olimpia</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1655,13 +1655,13 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="27">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CD Universidad Catolica de Chile</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1686,10 +1686,10 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
         <v>-8</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1720,10 +1720,10 @@
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I28" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="29">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1748,13 +1748,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="30">
@@ -1763,29 +1763,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="31">
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="32">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1841,13 +1841,13 @@
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I32" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="33">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1872,13 +1872,13 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="34">
@@ -1887,29 +1887,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I34" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="37">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>14</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2046,29 +2046,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2077,29 +2077,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="6">
@@ -2108,29 +2108,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="9">
@@ -2165,124 +2165,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CD Cobresal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Club Universidad de Chile</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Club Leon</t>
-        </is>
-      </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -2291,16 +2291,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -2309,16 +2309,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -2327,55 +2327,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Club Universidad de Chile</t>
+          <t>CD Cobresal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Club Leon</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2452,29 +2452,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2483,29 +2483,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -2514,29 +2514,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2545,29 +2545,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="9">
@@ -2602,16 +2602,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CA Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>SE Palmeiras</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Santos FC</t>
-        </is>
-      </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -2620,12 +2620,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2638,30 +2638,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2674,145 +2674,145 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Peniarol</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Velez Sarsfield</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC Recife</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2905,13 +2905,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2920,29 +2920,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2967,13 +2967,13 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2982,29 +2982,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="9">
@@ -3039,16 +3039,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3057,52 +3057,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -3111,34 +3111,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -3147,16 +3147,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3165,16 +3165,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -3183,73 +3183,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CA Boca Juniors</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCD Jorge Wilstermann</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Junior de Barranquilla</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3326,29 +3326,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3373,13 +3373,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3388,29 +3388,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -3419,29 +3419,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="9">
@@ -3476,34 +3476,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -3512,30 +3512,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3548,12 +3548,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3566,34 +3566,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3602,91 +3602,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Club Olimpia</t>
+          <t>CD Comerciantes Unidos</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CD Universidad Catolica</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3763,20 +3763,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
@@ -3794,29 +3794,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3825,29 +3825,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8</v>
-      </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3856,26 +3856,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
         <v>-7</v>
@@ -3913,16 +3913,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -3931,142 +3931,142 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -4075,16 +4075,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4093,37 +4093,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CDSC Guabira</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4200,29 +4200,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4231,29 +4231,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4262,29 +4262,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="6">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4309,13 +4309,13 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="9">
@@ -4350,217 +4350,217 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deportivo Tachira FC</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CR Flamengo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Club Sport Huancayo</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4637,29 +4637,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4668,29 +4668,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4699,29 +4699,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="6">
@@ -4730,29 +4730,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="9">
@@ -4787,106 +4787,106 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -4895,84 +4895,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4985,19 +4985,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Club Cerro Portenio</t>
+          <t>Montego Bay United FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5090,13 +5090,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -5105,29 +5105,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5155,10 +5155,10 @@
         <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5167,29 +5167,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5214,13 +5214,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5245,10 +5245,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5276,10 +5276,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5307,10 +5307,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>-1</v>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5338,10 +5338,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>-1</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5400,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5434,10 +5434,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5493,10 +5493,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>-2</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5527,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>-3</v>
@@ -5596,124 +5596,124 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Club Nacional</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CA Newells Old Boys</t>
+          <t>Club Leon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Santos FC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CCD Jorge Wilstermann</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior de Barranquilla</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>CA River Plate</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CS Defensa y Justicia</t>
+          <t>CF Monterrey</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -5722,34 +5722,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Sao Paulo FC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -5758,16 +5758,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
@@ -5776,109 +5776,109 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
